--- a/Vrindhavanam Glassmorphism/Vrindhavanam/coffee.xlsx
+++ b/Vrindhavanam Glassmorphism/Vrindhavanam/coffee.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Glassmorphism\Vrindavanam Glassmorphism\Vrindavanam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Glassmorphism\Vrindhavanam Glassmorphism\Vrindhavanam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5A1319-1AF3-4EBA-B369-0476BE235C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D47DC3F-A6DA-4C21-92BB-4A53D55CC476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD9E1797-03AD-478C-9B78-DB540EFC9CA1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="37">
   <si>
     <t>serial_no</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Pure</t>
+  </si>
+  <si>
+    <t>stock_quantity</t>
   </si>
 </sst>
 </file>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBA63B6-2881-429C-AD8E-0392E8073FB3}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
@@ -517,9 +520,10 @@
     <col min="12" max="12" width="16.88671875" customWidth="1"/>
     <col min="13" max="13" width="20.6640625" customWidth="1"/>
     <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,8 +566,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -606,8 +613,11 @@
       <c r="N2">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -650,8 +660,11 @@
       <c r="N3">
         <v>600</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -694,8 +707,11 @@
       <c r="N4">
         <v>900</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -738,8 +754,11 @@
       <c r="N5">
         <v>1600</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -782,8 +801,11 @@
       <c r="N6">
         <v>2000</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -826,8 +848,11 @@
       <c r="N7">
         <v>200</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -870,8 +895,11 @@
       <c r="N8">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -914,8 +942,11 @@
       <c r="N9">
         <v>900</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -958,8 +989,11 @@
       <c r="N10">
         <v>1600</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1002,8 +1036,11 @@
       <c r="N11">
         <v>2000</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1046,8 +1083,11 @@
       <c r="N12">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1090,8 +1130,11 @@
       <c r="N13">
         <v>600</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1134,8 +1177,11 @@
       <c r="N14">
         <v>900</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1178,8 +1224,11 @@
       <c r="N15">
         <v>1600</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1221,6 +1270,9 @@
       </c>
       <c r="N16">
         <v>2000</v>
+      </c>
+      <c r="O16">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
